--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD403F23-4179-499C-BC26-AD470B89D910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46161434-C140-4417-9E74-195AEEA25331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="924" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,11 +39,11 @@
     <t>QXDQC25320008</t>
   </si>
   <si>
-    <t>100000000000061</t>
+    <t>200000000000007</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>100000000000062</t>
+    <t>200000000000008</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46161434-C140-4417-9E74-195AEEA25331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC34CB16-4118-4D4E-A580-B642E4C7106E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,11 +39,11 @@
     <t>QXDQC25320008</t>
   </si>
   <si>
-    <t>200000000000007</t>
+    <t>200000000000011</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>200000000000008</t>
+    <t>200000000000012</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC34CB16-4118-4D4E-A580-B642E4C7106E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDF18E5-9D7F-4E31-BD37-2A5B01A597E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,11 +39,11 @@
     <t>QXDQC25320008</t>
   </si>
   <si>
-    <t>200000000000011</t>
+    <t>200000000000014</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>200000000000012</t>
+    <t>200000000000015</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDF18E5-9D7F-4E31-BD37-2A5B01A597E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F58293-4BFD-4982-97E6-FA124D03F49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>箱号</t>
   </si>
@@ -39,11 +39,11 @@
     <t>QXDQC25320008</t>
   </si>
   <si>
-    <t>200000000000014</t>
+    <t>200000000000030</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>200000000000015</t>
+    <t>200000000000031</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -516,9 +516,15 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F58293-4BFD-4982-97E6-FA124D03F49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E56EF99-BF65-4B17-939A-0D4B694486F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>箱号</t>
   </si>
@@ -516,15 +516,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/backend/data/c.xlsx
+++ b/backend/data/c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workstation\BaiduNetdiskWorkspace\else\qoder\TQ1\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E56EF99-BF65-4B17-939A-0D4B694486F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26A70E6-7209-4996-B882-498C913D2ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1128" windowWidth="19272" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>箱号</t>
   </si>
@@ -36,14 +37,63 @@
     <t>M101-SZ2507180003</t>
   </si>
   <si>
-    <t>QXDQC25320008</t>
-  </si>
-  <si>
-    <t>200000000000030</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>200000000000031</t>
+    <t>100000000000002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M101-SZ2507180006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M101-SZ2507180004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QXDQC25320001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QXDQC25320002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M101-SZ2507180005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QXDQC25320003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QXDQC25320004</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -474,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -498,10 +548,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -509,20 +559,82 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>